--- a/data/fmsForecastOutput/File1/RPT_RPT8758696367400AE_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT8758696367400AE_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>443.4826693607644</v>
+        <v>444.5528502254407</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>484.0977116286941</v>
+        <v>485.7019381129537</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>527.0813055023985</v>
+        <v>533.3806849354426</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>559.7245857367686</v>
+        <v>570.8748217038884</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>597.253810512755</v>
+        <v>613.5918082293813</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>38.25090990715531</v>
+        <v>38.34321428490721</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>44.13434334695889</v>
+        <v>44.28059787525316</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>50.70525129310629</v>
+        <v>51.31125194956795</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>57.43209229681958</v>
+        <v>58.57619315912494</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>66.03487987702341</v>
+        <v>67.84127725391458</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>45768259.81775468</v>
+        <v>45878704.53014242</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>53625827.83325035</v>
+        <v>53803535.70334337</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>62454794.63757282</v>
+        <v>63201219.23037812</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>71627802.53844027</v>
+        <v>73054695.19326012</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>83646847.68341909</v>
+        <v>85935023.97028349</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>450.9662520398815</v>
+        <v>452.05449175451</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>492.2666559866925</v>
+        <v>493.8979531151065</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>535.9755798469399</v>
+        <v>542.3812586465009</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>569.1697016438529</v>
+        <v>580.5080931320711</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>607.3322162322669</v>
+        <v>623.9459107577444</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>46.57938394509963</v>
+        <v>46.69178600459455</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>53.68676849829587</v>
+        <v>53.86467831652145</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>61.61293524298219</v>
+        <v>62.34929840560502</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>69.69052532211255</v>
+        <v>71.07882560731665</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>79.99241380256218</v>
+        <v>82.18062231802008</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>45768259.81775468</v>
+        <v>45878704.53014242</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>53625827.83325035</v>
+        <v>53803535.70334337</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>62454794.63757282</v>
+        <v>63201219.23037812</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>71627802.53844027</v>
+        <v>73054695.19326012</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>83646847.68341909</v>
+        <v>85935023.97028349</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>881.2266846643853</v>
+        <v>885.2287083975684</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>978.3936331962971</v>
+        <v>984.7023656403042</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1076.830698795232</v>
+        <v>1093.069685101484</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1135.974990457921</v>
+        <v>1162.121406176093</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1202.071068109859</v>
+        <v>1238.593187795069</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>57.61486757972671</v>
+        <v>57.87652110367338</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>65.02641382202776</v>
+        <v>65.44570748122328</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>74.04754098541748</v>
+        <v>75.16420399049262</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>83.07780039800058</v>
+        <v>84.98997868044837</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>94.7945009558062</v>
+        <v>97.67461029480852</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>15281293.46325167</v>
+        <v>15350692.29124672</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>17345717.63787507</v>
+        <v>17457563.71691093</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>19853448.29827567</v>
+        <v>20152845.29300129</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>22367040.03683541</v>
+        <v>22881855.88410363</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>25682956.38414068</v>
+        <v>26463272.98256487</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>895.0820100434429</v>
+        <v>899.1469566793968</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>993.776692257764</v>
+        <v>1000.18461545741</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1093.761461298921</v>
+        <v>1110.255769468451</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1153.83566511652</v>
+        <v>1180.393174942004</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1220.970956262652</v>
+        <v>1258.067304872812</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>57.8594451081017</v>
+        <v>58.12220936222734</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>65.30330806745478</v>
+        <v>65.72438715497935</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>74.36491852139721</v>
+        <v>75.48636769152731</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>83.43829065658437</v>
+        <v>85.35876624156299</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>95.212424221313</v>
+        <v>98.10523118188445</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>15281293.46325167</v>
+        <v>15350692.29124672</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>17345717.63787507</v>
+        <v>17457563.71691093</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>19853448.29827567</v>
+        <v>20152845.29300129</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>22367040.03683541</v>
+        <v>22881855.88410363</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>25682956.38414068</v>
+        <v>26463272.98256487</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>506.4552151357395</v>
+        <v>507.9471621532073</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>552.2923887222969</v>
+        <v>554.5456641887782</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>601.102965373508</v>
+        <v>608.7406749769852</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>636.5650044966173</v>
+        <v>649.7149140820602</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>677.3085466404946</v>
+        <v>696.3181522483782</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>41.76444147676695</v>
+        <v>41.8874737450412</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>47.89524604244684</v>
+        <v>48.09065192721416</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>54.87801535325548</v>
+        <v>55.57530411912089</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>61.98536156944768</v>
+        <v>63.26583079804404</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>71.10234016957372</v>
+        <v>73.0979261563819</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>61049553.28100636</v>
+        <v>61229396.82138915</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>70971545.47112544</v>
+        <v>71261099.42025431</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>82308242.93584849</v>
+        <v>83354064.52337942</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>93994842.57527569</v>
+        <v>95936551.07736376</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>109329804.0675598</v>
+        <v>112398296.9528484</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>514.9174341425547</v>
+        <v>516.4343096868321</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>561.5242405519014</v>
+        <v>563.8151806787376</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>611.153009623626</v>
+        <v>618.9184166831236</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>647.2089050293807</v>
+        <v>660.5786921271807</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>688.6344813880746</v>
+        <v>707.9619650941455</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>48.96904583562141</v>
+        <v>49.11330187188932</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>56.12694363513126</v>
+        <v>56.35593369127564</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>64.27133039560621</v>
+        <v>65.08797211203121</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>72.53443251653408</v>
+        <v>74.03282030519063</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>83.11345205833511</v>
+        <v>85.44614659197917</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>61049553.28100636</v>
+        <v>61229396.82138915</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>70971545.47112544</v>
+        <v>71261099.42025431</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>82308242.93584849</v>
+        <v>83354064.52337942</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>93994842.57527569</v>
+        <v>95936551.07736376</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>109329804.0675598</v>
+        <v>112398296.9528484</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>891.3947010560468</v>
+        <v>895.1415248004108</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>974.3311947755478</v>
+        <v>980.0729693259422</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1061.699815021288</v>
+        <v>1077.029250425972</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1133.431450800131</v>
+        <v>1158.821865496601</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1219.361703952043</v>
+        <v>1255.711944995722</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>89.27996919275746</v>
+        <v>89.65524213085236</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>101.1247656025734</v>
+        <v>101.720698082889</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>114.4891849590058</v>
+        <v>116.1422459660182</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>128.8574239897535</v>
+        <v>131.7440065259176</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>146.8939287861138</v>
+        <v>151.2729655410997</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>5605932.496101831</v>
+        <v>5629496.065596705</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>6428189.345706714</v>
+        <v>6466070.934829802</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>7361192.68722243</v>
+        <v>7467477.840712775</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>8374037.947878093</v>
+        <v>8561627.851114416</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>9674380.582872598</v>
+        <v>9962782.346677324</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1132.024251457969</v>
+        <v>1136.782519977553</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1237.349223785199</v>
+        <v>1244.640974599681</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1348.302763016953</v>
+        <v>1367.770337390799</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1439.398156788308</v>
+        <v>1471.642644170752</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1548.525045681235</v>
+        <v>1594.687934420687</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>102.2111735361745</v>
+        <v>102.6408005594123</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>115.8175997626957</v>
+        <v>116.5001177302728</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>131.1819336447159</v>
+        <v>133.0760142027198</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>147.7398256443604</v>
+        <v>151.0493998031209</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>168.5446406658589</v>
+        <v>173.5691041166687</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>5605932.496101831</v>
+        <v>5629496.065596705</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>6428189.345706714</v>
+        <v>6466070.934829802</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>7361192.68722243</v>
+        <v>7467477.840712775</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>8374037.947878093</v>
+        <v>8561627.851114416</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>9674380.582872598</v>
+        <v>9962782.346677324</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>525.5424118668298</v>
+        <v>527.1461667846686</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>572.9022709483426</v>
+        <v>575.3259041028705</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>623.3013323322406</v>
+        <v>631.3097430206508</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>660.2413178815325</v>
+        <v>673.9745029872976</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>702.7031942079863</v>
+        <v>722.5251912198281</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>43.7214279741694</v>
+        <v>43.85484909023011</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>50.08477099359556</v>
+        <v>50.29665200310192</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>57.32841466128745</v>
+        <v>58.06499176277573</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>64.73345193624019</v>
+        <v>66.07992398198853</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>74.21528525673742</v>
+        <v>76.30876536998795</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>66655485.77710818</v>
+        <v>66858892.88698585</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>77399734.81683214</v>
+        <v>77727170.35508411</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>89669435.62307094</v>
+        <v>90821542.3640922</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>102368880.5231538</v>
+        <v>104498178.9284782</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>119004184.6504324</v>
+        <v>122361079.2995257</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>539.6595267159731</v>
+        <v>541.3063616818797</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>588.2063942372233</v>
+        <v>590.6947706865237</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>639.8717222332704</v>
+        <v>648.0930355431109</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>677.7205504694525</v>
+        <v>691.8173079996258</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>721.1908606362679</v>
+        <v>741.534361565721</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>51.21265003066139</v>
+        <v>51.36893149812749</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>58.63681433110661</v>
+        <v>58.88487431357713</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>67.08011519817072</v>
+        <v>67.94198582745805</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>75.68605540325967</v>
+        <v>77.26034434978189</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>86.68542807725279</v>
+        <v>89.13066855784322</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>66655485.77710818</v>
+        <v>66858892.88698585</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>77399734.81683214</v>
+        <v>77727170.35508411</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>89669435.62307094</v>
+        <v>90821542.3640922</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>102368880.5231538</v>
+        <v>104498178.9284782</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>119004184.6504324</v>
+        <v>122361079.2995257</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>2992.005633317737</v>
+        <v>2998.157856526886</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>3112.054111500075</v>
+        <v>3121.276656872475</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>3307.722287153533</v>
+        <v>3346.900331259475</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>3469.630894069584</v>
+        <v>3539.56457792644</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3695.385140586401</v>
+        <v>3799.993001433379</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2655.868210096912</v>
+        <v>2661.329260657997</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2759.185740881357</v>
+        <v>2767.362563897424</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>2933.355711025158</v>
+        <v>2968.099601064324</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>3074.967999833879</v>
+        <v>3136.946880739596</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3292.912981338576</v>
+        <v>3386.127780291416</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>65207274.24222937</v>
+        <v>65341354.77387379</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>74794356.03350759</v>
+        <v>75016008.45901313</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>88025279.73288214</v>
+        <v>89067887.90624863</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>102424071.6659591</v>
+        <v>104488525.4553988</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>122220863.6761782</v>
+        <v>125680655.447167</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>2180.673383629697</v>
+        <v>2185.157328864607</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>2268.168713919963</v>
+        <v>2274.890412234618</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>2410.778198982241</v>
+        <v>2439.332462735335</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>2528.782585655433</v>
+        <v>2579.752584276965</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>2693.319801474345</v>
+        <v>2769.561495449531</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>1926.186866041372</v>
+        <v>1930.147530891215</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>2001.027514742669</v>
+        <v>2006.957542430151</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>2127.359074101697</v>
+        <v>2152.556403381132</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>2230.005282206311</v>
+        <v>2274.953142415734</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>2388.566174501259</v>
+        <v>2456.180993660914</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>65207274.24222937</v>
+        <v>65341354.77387379</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>74794356.03350759</v>
+        <v>75016008.45901313</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>88025279.73288214</v>
+        <v>89067887.90624863</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>102424071.6659591</v>
+        <v>104488525.4553988</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>122220863.6761782</v>
+        <v>125680655.447167</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>887.2141613875779</v>
+        <v>889.4848844848933</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>956.3842863523615</v>
+        <v>959.834742920214</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>1042.355791489744</v>
+        <v>1055.22997177754</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>1109.580926965817</v>
+        <v>1132.302936673623</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>1191.670822238225</v>
+        <v>1225.345792426896</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>85.12207771440467</v>
+        <v>85.33993792941214</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>96.78590093043989</v>
+        <v>97.13508645377661</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>111.4671416337965</v>
+        <v>112.8438769954408</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>126.8303638726817</v>
+        <v>129.4275973769022</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>147.0332174062268</v>
+        <v>151.1881728859619</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>131862760.0193376</v>
+        <v>132200247.6608596</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>152194090.8503397</v>
+        <v>152743178.8140972</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>177694715.3559531</v>
+        <v>179889430.2703408</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>204792952.1891128</v>
+        <v>208986704.383877</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>241225048.3266106</v>
+        <v>248041734.7466927</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>859.5093506642763</v>
+        <v>861.7091664695826</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>924.845311304806</v>
+        <v>928.1819811185795</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>1005.915160794637</v>
+        <v>1018.33926131773</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>1069.123916450676</v>
+        <v>1091.017447078378</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>1146.561769738528</v>
+        <v>1178.962020457846</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>98.74428153956389</v>
+        <v>98.99700622609168</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>112.1248011616784</v>
+        <v>112.5293265832148</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>128.939093192049</v>
+        <v>130.5316253633596</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>146.4400814694956</v>
+        <v>149.4388829736461</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>169.3999510171</v>
+        <v>174.1869594711198</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>131862760.0193376</v>
+        <v>132200247.6608596</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>152194090.8503397</v>
+        <v>152743178.8140972</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>177694715.3559531</v>
+        <v>179889430.2703408</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>204792952.1891128</v>
+        <v>208986704.383877</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>241225048.3266106</v>
+        <v>248041734.7466927</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="C23" s="85" t="n">
-        <v>126831.7918250114</v>
+        <v>126831.7918250115</v>
       </c>
       <c r="D23" s="86" t="n">
         <v>135101.1136484238</v>
@@ -3715,7 +3715,7 @@
         <v>155047.6738590327</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>169351.9904723949</v>
+        <v>169351.990472395</v>
       </c>
       <c r="H23" s="85" t="n">
         <v>1397717.813839474</v>
@@ -3896,7 +3896,7 @@
         <v>32975.65810448211</v>
       </c>
       <c r="V24" s="80" t="n">
-        <v>36513.22206665209</v>
+        <v>36513.2220666521</v>
       </c>
       <c r="W24" s="80" t="n">
         <v>40503.3126402252</v>
@@ -3926,7 +3926,7 @@
         <v>37377.97480667131</v>
       </c>
       <c r="AF24" s="80" t="n">
-        <v>41377.72546463594</v>
+        <v>41377.72546463595</v>
       </c>
       <c r="AG24" s="80" t="n">
         <v>45929.96818582567</v>
@@ -4034,7 +4034,7 @@
         <v>1398476.087516877</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>1423997.15512468</v>
+        <v>1423997.155124681</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>455.9570601309058</v>
+        <v>457.0578596331059</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>509.4239498391403</v>
+        <v>511.1128957260927</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>558.1979235466482</v>
+        <v>564.872398123513</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>600.2901078628599</v>
+        <v>612.2539713889358</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>642.1502042819843</v>
+        <v>659.7247269037434</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>39.32684100990416</v>
+        <v>39.42178628171194</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>46.44329227610406</v>
+        <v>46.59727052445894</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>53.69867170254653</v>
+        <v>54.34075653298231</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>61.59443011470849</v>
+        <v>62.82201548752485</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>70.9988129943648</v>
+        <v>72.94192573771851</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>47055640.80754391</v>
+        <v>47169245.42189462</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>56431336.83962008</v>
+        <v>56618429.48471577</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>66141857.65703816</v>
+        <v>66932727.93579801</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>76818961.33824845</v>
+        <v>78349973.68982242</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>89934696.74364595</v>
+        <v>92396051.3486321</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>463.6511428839818</v>
+        <v>464.7705179127063</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>518.0202637668946</v>
+        <v>519.737709902129</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>567.6172776742717</v>
+        <v>574.404381189732</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>610.4197498173539</v>
+        <v>622.5854984858372</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>652.9862176781401</v>
+        <v>670.8573029441069</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>47.889580435982</v>
+        <v>48.00519839853613</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>56.4954656994506</v>
+        <v>56.68277095758516</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>65.25029849705086</v>
+        <v>66.03050824001134</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>74.7412817458488</v>
+        <v>76.23088566045405</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>86.00555402103598</v>
+        <v>88.35937489450235</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>47055640.80754391</v>
+        <v>47169245.42189462</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>56431336.83962008</v>
+        <v>56618429.48471577</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>66141857.65703816</v>
+        <v>66932727.93579801</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>76818961.33824845</v>
+        <v>78349973.68982242</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>89934696.74364595</v>
+        <v>92396051.3486321</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>906.364462748077</v>
+        <v>910.4808309198252</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1029.978957210314</v>
+        <v>1036.620581548258</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1140.856746064072</v>
+        <v>1158.061899190478</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1218.790236143097</v>
+        <v>1246.843734578342</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1292.9663330623</v>
+        <v>1332.251300151237</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>59.25838312543677</v>
+        <v>59.52751252341341</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>68.45489956913995</v>
+        <v>68.89631803099023</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>78.4502491962606</v>
+        <v>79.63335001490675</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>89.13436723154597</v>
+        <v>91.18601710328248</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>101.9624392824151</v>
+        <v>105.0604248749947</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>15717206.00493474</v>
+        <v>15788587.67225139</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>18260262.08526919</v>
+        <v>18378009.92878945</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>21033891.81703589</v>
+        <v>21351101.95827832</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>23997649.80506105</v>
+        <v>24550015.59475284</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>27624987.25671559</v>
+        <v>28464333.717224</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>920.615023655878</v>
+        <v>924.7961125418217</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1046.173080509208</v>
+        <v>1052.919129585814</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1158.794175448238</v>
+        <v>1176.269841257603</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1237.95299594651</v>
+        <v>1266.447573113942</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1313.295346652677</v>
+        <v>1353.197982283653</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>59.50993744620757</v>
+        <v>59.78020930976185</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>68.74639292772893</v>
+        <v>69.18969102932446</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>78.78649732085137</v>
+        <v>79.97466906579217</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>89.52113807692305</v>
+        <v>91.58169044474447</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>102.4119640455004</v>
+        <v>105.5236078170069</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>15717206.00493474</v>
+        <v>15788587.67225139</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>18260262.08526919</v>
+        <v>18378009.92878945</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>21033891.81703589</v>
+        <v>21351101.95827832</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>23997649.80506105</v>
+        <v>24550015.59475284</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>27624987.25671559</v>
+        <v>28464333.717224</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>520.7513229582903</v>
+        <v>522.285933156792</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>581.2414160333866</v>
+        <v>583.6136495886708</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>636.6507125946796</v>
+        <v>644.7431028897176</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>682.764338632505</v>
+        <v>696.8736831404326</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>728.2934364777361</v>
+        <v>748.7415938729818</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>42.9433590605072</v>
+        <v>43.06990951533428</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>50.40572928296697</v>
+        <v>50.61145131014054</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>58.12336586748051</v>
+        <v>58.86216494923131</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>66.48401042769784</v>
+        <v>67.85790439713368</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>76.45462015879991</v>
+        <v>78.60122210287588</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>62772846.81247865</v>
+        <v>62957833.09414601</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>74691598.92488927</v>
+        <v>74996439.41350523</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>87175749.47407405</v>
+        <v>88283829.89407633</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>100816611.1433095</v>
+        <v>102899989.2845753</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>117559684.0003615</v>
+        <v>120860385.0658561</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>529.4524116454327</v>
+        <v>531.0126632179428</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>590.9571657696151</v>
+        <v>593.3690524309982</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>647.2950916811642</v>
+        <v>655.5227813928401</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>694.1807307627465</v>
+        <v>708.5259953392674</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>740.4719391402987</v>
+        <v>761.2620300568553</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>50.35133342653079</v>
+        <v>50.49971455659794</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>59.06890057200008</v>
+        <v>59.30997979337923</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>68.07217840016025</v>
+        <v>68.93743563611383</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>77.79869062138903</v>
+        <v>79.40640277935177</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>89.36987716651596</v>
+        <v>91.87909834463454</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>62772846.81247865</v>
+        <v>62957833.09414601</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>74691598.92488927</v>
+        <v>74996439.41350523</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>87175749.47407405</v>
+        <v>88283829.89407633</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>100816611.1433095</v>
+        <v>102899989.2845753</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>117559684.0003615</v>
+        <v>120860385.0658561</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>916.6364197805945</v>
+        <v>920.4903537915262</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1025.500360029521</v>
+        <v>1031.545243891889</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1124.606150007461</v>
+        <v>1140.848125070669</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1215.82464269877</v>
+        <v>1243.068044229542</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1311.311230611163</v>
+        <v>1350.413107680353</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>91.8081195928328</v>
+        <v>92.1941204399988</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>106.4355571179569</v>
+        <v>107.0629489811699</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>121.2727361280156</v>
+        <v>123.0242015241679</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>138.2245316828189</v>
+        <v>141.3217763723814</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>157.9708940353955</v>
+        <v>162.6814145700233</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>5764676.283884912</v>
+        <v>5788913.46398495</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>6765779.976775518</v>
+        <v>6805661.341806697</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>7797347.659210338</v>
+        <v>7909959.817910711</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>8982776.760550831</v>
+        <v>9184056.933327857</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>10403905.47481582</v>
+        <v>10714138.63946744</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1164.079902799419</v>
+        <v>1168.97419570774</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1302.331364609835</v>
+        <v>1310.008048262251</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1428.190490294579</v>
+        <v>1448.816941900522</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1544.03316446088</v>
+        <v>1578.630847382379</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1665.296094426409</v>
+        <v>1714.953415776211</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>105.1054982274134</v>
+        <v>105.5474069772878</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>121.9000180752297</v>
+        <v>122.6185662891612</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>138.9545399362813</v>
+        <v>140.961372437197</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>158.4795627469387</v>
+        <v>162.0306688939177</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>181.25424100834</v>
+        <v>186.6590456685381</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>5764676.283884912</v>
+        <v>5788913.46398495</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>6765779.976775518</v>
+        <v>6805661.341806697</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>7797347.659210338</v>
+        <v>7909959.817910711</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>8982776.760550831</v>
+        <v>9184056.933327857</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>10403905.47481582</v>
+        <v>10714138.63946744</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>540.3812570189349</v>
+        <v>542.0308707219098</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>602.9363985380819</v>
+        <v>605.4879826393368</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>660.1676208572542</v>
+        <v>668.6527786525118</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>708.1653350290729</v>
+        <v>722.9005339338947</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>755.6072362552831</v>
+        <v>776.9293017360236</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>44.9559154006609</v>
+        <v>45.09315164472277</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>52.71044116214716</v>
+        <v>52.93350801292208</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>60.71920779127564</v>
+        <v>61.49963391796598</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>69.43216886986974</v>
+        <v>70.8768834980557</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>79.80269200845977</v>
+        <v>82.05460033185874</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>68537523.09636356</v>
+        <v>68746746.55813096</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>81457378.90166478</v>
+        <v>81802100.75531192</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>94973097.13328439</v>
+        <v>96193789.71198705</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>109799387.9038603</v>
+        <v>112084046.2179031</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>127963589.4751774</v>
+        <v>131574523.7053235</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>554.8969727735633</v>
+        <v>556.5908983828197</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>619.042833171874</v>
+        <v>621.6625785628422</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>677.7180965424384</v>
+        <v>686.4288312228168</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>726.9133083328226</v>
+        <v>742.0386069813458</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>775.4867738037474</v>
+        <v>797.3698090330519</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>52.65865432351092</v>
+        <v>52.8194046023631</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>61.71082128199738</v>
+        <v>61.97197710347426</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>71.04769035469023</v>
+        <v>71.96086883330953</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>81.17977371312516</v>
+        <v>82.86892743689819</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>93.21166784631458</v>
+        <v>95.84195669219417</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>68537523.09636356</v>
+        <v>68746746.55813096</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>81457378.90166478</v>
+        <v>81802100.75531192</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>94973097.13328439</v>
+        <v>96193789.71198705</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>109799387.9038603</v>
+        <v>112084046.2179031</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>127963589.4751774</v>
+        <v>131574523.7053235</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>3077.561852826309</v>
+        <v>3083.889998484762</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>3276.191295399594</v>
+        <v>3285.900259893121</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>3504.68561893784</v>
+        <v>3546.196578999231</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>3722.77992925921</v>
+        <v>3797.816070736524</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>3974.814607493171</v>
+        <v>4087.332474382466</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>2731.81260038769</v>
+        <v>2737.429809358153</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>2904.711802170078</v>
+        <v>2913.319890406804</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>3108.026818208475</v>
+        <v>3144.839585785468</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>3299.321888233776</v>
+        <v>3365.822833411584</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>3541.909197954798</v>
+        <v>3642.172507573858</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67209786.84825529</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78972532.32868001</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>94371570.14859995</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>112112151.776179</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>131462690.8423989</v>
+        <v>135184097.5015242</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>2243.029606695841</v>
+        <v>2247.641770072626</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>2387.797361743303</v>
+        <v>2394.87357851839</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>2554.331636980548</v>
+        <v>2584.586207602601</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>2713.28603611098</v>
+        <v>2767.974875833654</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>2896.977306092659</v>
+        <v>2978.984075991752</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>1981.266062581127</v>
+        <v>1985.339982401991</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>2106.56649620241</v>
+        <v>2112.809287746237</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>2254.035891186371</v>
+        <v>2280.733633588824</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>2392.709530264282</v>
+        <v>2440.936848085552</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>2569.179492848509</v>
+        <v>2641.90705997732</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67209786.84825529</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78972532.32868001</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>94371570.14859995</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>112112151.776179</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>131462690.8423989</v>
+        <v>135184097.5015242</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>912.4227036357422</v>
+        <v>914.7583575045752</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>1006.671677053116</v>
+        <v>1010.304223156724</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1104.214203457709</v>
+        <v>1117.854890113678</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1190.329060128791</v>
+        <v>1214.708917144612</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1281.586348187484</v>
+        <v>1317.808692247784</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>87.54066342426205</v>
+        <v>87.76475329882605</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>101.8749749395672</v>
+        <v>102.2425878879668</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>118.0821385708982</v>
+        <v>119.5408423684662</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>136.0602585673435</v>
+        <v>138.8469918838002</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>158.1273625580411</v>
+        <v>162.5966234393121</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>135609395.388309</v>
+        <v>135956533.4063863</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>160196568.3252963</v>
+        <v>160774633.0839919</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>188239975.4262301</v>
+        <v>190565359.860587</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>219696460.5068207</v>
+        <v>224196197.9940821</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>259426280.3175762</v>
+        <v>266758621.2068477</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>883.9307121820254</v>
+        <v>886.1934311821792</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>973.4743594510561</v>
+        <v>976.9871139786674</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1065.611010263007</v>
+        <v>1078.774820185603</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1146.927849697213</v>
+        <v>1170.418779995139</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1233.073667685077</v>
+        <v>1267.924864957702</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>101.549916865607</v>
+        <v>101.8098681527262</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>118.0204058508424</v>
+        <v>118.4462791272961</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>136.5909598680621</v>
+        <v>138.278308643113</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>157.0970447531298</v>
+        <v>160.3146453452509</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>182.1817405912315</v>
+        <v>187.3308666712127</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>135609395.388309</v>
+        <v>135956533.4063863</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>160196568.3252963</v>
+        <v>160774633.0839919</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>188239975.4262301</v>
+        <v>190565359.860587</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>219696460.5068207</v>
+        <v>224196197.9940821</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>259426280.3175762</v>
+        <v>266758621.2068477</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5383,7 +5383,7 @@
         <v>0.2491675177064494</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2727982514695381</v>
+        <v>0.272798251469538</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.01567154303209634</v>
@@ -5652,7 +5652,7 @@
         <v>0.02523141550445889</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.02968995016641673</v>
+        <v>0.02968995016641672</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>19450.72208792473</v>
@@ -5686,7 +5686,7 @@
         <v>0.2371588319298149</v>
       </c>
       <c r="F49" s="156" t="n">
-        <v>0.24735790654064</v>
+        <v>0.2473579065406401</v>
       </c>
       <c r="G49" s="157" t="n">
         <v>0.2573797525925846</v>
@@ -5701,7 +5701,7 @@
         <v>0.02557419808246827</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.0281215971356928</v>
+        <v>0.02812159713569281</v>
       </c>
       <c r="L49" s="157" t="n">
         <v>0.03100599512497865</v>
@@ -5713,7 +5713,7 @@
         <v>1486.827400324131</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>1644.317757818354</v>
+        <v>1644.317757818355</v>
       </c>
       <c r="P49" s="159" t="n">
         <v>1827.533985065208</v>
@@ -5733,16 +5733,16 @@
         <v>0.2861964125127009</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.301179207004412</v>
+        <v>0.3011792070044121</v>
       </c>
       <c r="W49" s="156" t="n">
-        <v>0.3141314937840004</v>
+        <v>0.3141314937840005</v>
       </c>
       <c r="X49" s="157" t="n">
         <v>0.3268587096421819</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.02467620097747285</v>
+        <v>0.02467620097747286</v>
       </c>
       <c r="Z49" s="156" t="n">
         <v>0.02678838028969382</v>
@@ -5751,7 +5751,7 @@
         <v>0.02930296653847631</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.03224245626700228</v>
+        <v>0.03224245626700229</v>
       </c>
       <c r="AC49" s="157" t="n">
         <v>0.03557597206373389</v>
@@ -5763,7 +5763,7 @@
         <v>1486.827400324131</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>1644.317757818354</v>
+        <v>1644.317757818355</v>
       </c>
       <c r="AG49" s="159" t="n">
         <v>1827.533985065208</v>
@@ -5791,7 +5791,7 @@
         <v>0.2226672927133033</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.2426723784433134</v>
+        <v>0.2426723784433133</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.01364608081366838</v>
@@ -6334,46 +6334,46 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.01035805149502584</v>
+        <v>0.01032908329305596</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.009566382072503392</v>
+        <v>0.009526065205056349</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.008856602732167733</v>
+        <v>0.008706877554368784</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0003219019782294294</v>
+        <v>0.0003116484137580209</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.000893394312614286</v>
+        <v>0.0008908957705961292</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.0008721503548438408</v>
+        <v>0.0008684747364142571</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008520056819502073</v>
+        <v>0.0008376021114081553</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.302964457040277e-05</v>
+        <v>3.197754917188071e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01053283923784634</v>
+        <v>0.01050338220970695</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009727810728290084</v>
+        <v>0.009686813530738286</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.009006054161459897</v>
+        <v>0.008853802434542764</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003273339381121539</v>
+        <v>0.0003169073490723039</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.001087915471883842</v>
+        <v>0.001084872915556445</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.001060918338086801</v>
+        <v>0.001056447169813925</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.001035288645059688</v>
+        <v>0.001017786586861707</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>4.007956508736669e-05</v>
+        <v>3.880290811598137e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.008867973163611882</v>
+        <v>0.008843172240601375</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.00824657280861252</v>
+        <v>0.008211818187659958</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.007664094940340387</v>
+        <v>0.007534529686900412</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002789777865861412</v>
+        <v>0.0002700914891592486</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.0007312906159134787</v>
+        <v>0.0007292454267897682</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0007151495145337731</v>
+        <v>0.0007121355654813775</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006996976292463717</v>
+        <v>0.0006878689004309861</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>2.716539371349948e-05</v>
+        <v>2.630009267569711e-05</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.009016145655106379</v>
+        <v>0.008990930340386963</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008384418521908119</v>
+        <v>0.008349082959560059</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007792233541752317</v>
+        <v>0.007660502042917862</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002836425290559563</v>
+        <v>0.000274607645286352</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0008574424180854412</v>
+        <v>0.0008550444221731242</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.0008380613904218285</v>
+        <v>0.0008345294376173049</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0008194628981539542</v>
+        <v>0.0008056094792035807</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.178857664465285e-05</v>
+        <v>3.077601306280389e-05</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.008428255351927238</v>
+        <v>0.00840468418090095</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.007843858906676757</v>
+        <v>0.007810801496109518</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.00729472551885533</v>
+        <v>0.007171404635178546</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002656841428881551</v>
+        <v>0.000257221288751257</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0007011714963369497</v>
+        <v>0.0006992105408878321</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0006857327976666432</v>
+        <v>0.0006828428233693504</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006709355935762729</v>
+        <v>0.0006595931009662128</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.604903878032898e-05</v>
+        <v>2.521929706820457e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,46 +6792,46 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008654655060294093</v>
+        <v>0.008630450720714718</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.008053394441541462</v>
+        <v>0.008019453957695261</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.00748865490709542</v>
+        <v>0.00736205555276654</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002727178664717759</v>
+        <v>0.0002640309666839769</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.0008213101016415637</v>
+        <v>0.0008190131564182577</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.0008028226133383116</v>
+        <v>0.0007994391719662087</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007850633437809199</v>
+        <v>0.0007717914660321179</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>3.045641678851816e-05</v>
+        <v>2.948628658047519e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.007192371584422295</v>
+        <v>0.007172256790360879</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.00665921969997868</v>
+        <v>0.006631154870881326</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.006155974440520871</v>
+        <v>0.006051904697809585</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002231900687600514</v>
+        <v>0.0002160807811067205</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006900584318926566</v>
+        <v>0.0006881285561785144</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.000673911718702904</v>
+        <v>0.0006710715635399558</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006583058111807137</v>
+        <v>0.0006471768311862606</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>2.551168368675305e-05</v>
+        <v>2.469905838107735e-05</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6996,46 +6996,46 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.006967777228211354</v>
+        <v>0.006948290553702651</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006439616589648573</v>
+        <v>0.006412477262943142</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.005940762328699693</v>
+        <v>0.005840330851436384</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002150522189293119</v>
+        <v>0.0002082021467314345</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0008004894371372666</v>
+        <v>0.0007982507207434657</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.000780715132407505</v>
+        <v>0.000777424861512132</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.000761492158967874</v>
+        <v>0.0007486187635653838</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>2.945614065463395e-05</v>
+        <v>2.851787230678957e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1068.970728243674</v>
+        <v>1065.981154386996</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1059.714073593138</v>
+        <v>1055.247980611171</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1049.434497201277</v>
+        <v>1031.693296491086</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>41.19370833603931</v>
+        <v>39.88156248790497</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.004396391220535033</v>
+        <v>0.004384095901393568</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.006412249531952774</v>
+        <v>0.006385225541853093</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.008483086307659218</v>
+        <v>0.008339675606727029</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.01035731027260416</v>
+        <v>0.010027398200567</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01206934436206962</v>
+        <v>0.01149856090380876</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.0003791939936135237</v>
+        <v>0.0003781335076526229</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005845935968535278</v>
+        <v>0.0005821298668481711</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0008160733808628933</v>
+        <v>0.0008022772633512771</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.001062740523966812</v>
+        <v>0.001028888981522714</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.001334437204275779</v>
+        <v>0.001271328997281355</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>453.7159838330874</v>
+        <v>452.4470833779243</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>710.3156680238225</v>
+        <v>707.3220908892037</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>1005.175876485817</v>
+        <v>988.1828892900128</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1325.42217001049</v>
+        <v>1283.203412155106</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1690.341010342051</v>
+        <v>1610.401399823081</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004470578464956651</v>
+        <v>0.004458075667499304</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006520453533702529</v>
+        <v>0.006492973525187243</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008626234805094212</v>
+        <v>0.008480404109173169</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01053208550760946</v>
+        <v>0.01019660630874073</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01227300944901986</v>
+        <v>0.01169259426105032</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.000461756927118117</v>
+        <v>0.0004604655386815783</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0007111228743822255</v>
+        <v>0.0007081258953312387</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009916266084152702</v>
+        <v>0.000974862678187725</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.001289574215990136</v>
+        <v>0.001248497325325931</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.001616491969649268</v>
+        <v>0.001540044828113811</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>453.7159838330874</v>
+        <v>452.4470833779243</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>710.3156680238225</v>
+        <v>707.3220908892037</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>1005.175876485817</v>
+        <v>988.1828892900128</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1325.42217001049</v>
+        <v>1283.203412155106</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1690.341010342051</v>
+        <v>1610.401399823081</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003763939518853137</v>
+        <v>0.003753412967576873</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.005527594678058093</v>
+        <v>0.005504299005749876</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.007340871078349563</v>
+        <v>0.007216770081540367</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.008976209188679193</v>
+        <v>0.008690289418532959</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.01047182351423703</v>
+        <v>0.00997659001517987</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.0003103903900270825</v>
+        <v>0.0003095223260372353</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004793575152121664</v>
+        <v>0.000477337295524715</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.000670188734626547</v>
+        <v>0.0006588588680303682</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.000874056173608323</v>
+        <v>0.0008462148059441007</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.001099308670174259</v>
+        <v>0.001047320162295559</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>453.7159838330874</v>
+        <v>452.4470833779243</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>710.3156680238225</v>
+        <v>707.3220908892037</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>1005.175876485817</v>
+        <v>988.1828892900128</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1325.42217001049</v>
+        <v>1283.203412155106</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1690.341010342051</v>
+        <v>1610.401399823081</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003826830135012366</v>
+        <v>0.003816127698525281</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005619991271029431</v>
+        <v>0.005596306199556185</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007463605590440984</v>
+        <v>0.007337429706996283</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.009126298931424524</v>
+        <v>0.008835598343023611</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.01064693305685052</v>
+        <v>0.01014341827694587</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.000363934502622953</v>
+        <v>0.0003629166926438413</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005617441074119461</v>
+        <v>0.0005593766750277868</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007849030493053503</v>
+        <v>0.0007716338814126387</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.00102280872346322</v>
+        <v>0.000990229131235691</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.001285011692131879</v>
+        <v>0.001224240916558873</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>453.7159838330874</v>
+        <v>452.4470833779243</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>710.3156680238225</v>
+        <v>707.3220908892037</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>1005.175876485817</v>
+        <v>988.1828892900128</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1325.42217001049</v>
+        <v>1283.203412155106</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1690.341010342051</v>
+        <v>1610.401399823081</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.01198264253573046</v>
+        <v>0.01192393755569502</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01787647302587098</v>
+        <v>0.01774231566994844</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.02409967911131485</v>
+        <v>0.02361332313416544</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02996632524770066</v>
+        <v>0.02893354052902598</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03564412007955492</v>
+        <v>0.03387600115670168</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001200152923469731</v>
+        <v>0.001194273172554881</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.001855379520059782</v>
+        <v>0.001841455475295256</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.002598806725018305</v>
+        <v>0.002546360168434268</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003406808126889306</v>
+        <v>0.003289393016967612</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004293971853995306</v>
+        <v>0.004080970302202107</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.35818319386652</v>
+        <v>74.98899078687349</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>117.9407516252103</v>
+        <v>117.0556430598542</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>167.0927875550782</v>
+        <v>163.7206855619105</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>221.3977251165527</v>
+        <v>213.7672871045625</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>282.7994204456233</v>
+        <v>268.7712159185982</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01521732396538649</v>
+        <v>0.01514277173728512</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.02270217780276865</v>
+        <v>0.02253180503721835</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.03060532127243162</v>
+        <v>0.02998767483553627</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.03805565241445327</v>
+        <v>0.03674407029859612</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04526615236116276</v>
+        <v>0.04302073459307378</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001373981642689264</v>
+        <v>0.001367250275658776</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.002124955260778551</v>
+        <v>0.002109008134137452</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.002977717864607576</v>
+        <v>0.002917624496765325</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003906032132928865</v>
+        <v>0.003771411345621927</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.004926860824961244</v>
+        <v>0.004682464951660531</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.35818319386652</v>
+        <v>74.98899078687349</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>117.9407516252103</v>
+        <v>117.0556430598542</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>167.0927875550782</v>
+        <v>163.7206855619105</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>221.3977251165527</v>
+        <v>213.7672871045625</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>282.7994204456233</v>
+        <v>268.7712159185982</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.004171463316996358</v>
+        <v>0.004158547841794241</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.006130640949447833</v>
+        <v>0.006101931447392443</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.008148558258127712</v>
+        <v>0.008006998459782271</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.009976414715730537</v>
+        <v>0.009654905887983166</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.01165112039890257</v>
+        <v>0.01109625349250318</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003470363739304849</v>
+        <v>0.0003459618973401072</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005359583362949179</v>
+        <v>0.0005334484687159255</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007494672359605999</v>
+        <v>0.0007364472111380156</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009781389698071269</v>
+        <v>0.0009466165920273773</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001230521265724053</v>
+        <v>0.001171919560085918</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>529.0741670269539</v>
+        <v>527.4360741647978</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>828.2564196490328</v>
+        <v>824.3777339490579</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>1172.268664040896</v>
+        <v>1151.903574851923</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1546.819895127043</v>
+        <v>1496.970699259668</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1973.140430787675</v>
+        <v>1879.172615741679</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004283517121609084</v>
+        <v>0.004270254711045246</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006294410740017698</v>
+        <v>0.006264934311766867</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.008365186685606285</v>
+        <v>0.008219863537286733</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.01024053037842387</v>
+        <v>0.009910509924052924</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01195765383894682</v>
+        <v>0.01138818874320924</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0004064975274026214</v>
+        <v>0.0004052389501754169</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006274739572744082</v>
+        <v>0.000624535526364065</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008769534064830986</v>
+        <v>0.0008617186442776162</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.00114363560178789</v>
+        <v>0.001106779782119405</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.001437281583011486</v>
+        <v>0.00136883323141214</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>529.0741670269539</v>
+        <v>527.4360741647978</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>828.2564196490328</v>
+        <v>824.3777339490579</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>1172.268664040896</v>
+        <v>1151.903574851923</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1546.819895127043</v>
+        <v>1496.970699259668</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1973.140430787675</v>
+        <v>1879.172615741679</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003559777554647064</v>
+        <v>0.00354875595017921</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.005204744943755706</v>
+        <v>0.00518037136897084</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006876518689355814</v>
+        <v>0.006757057237630546</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.008380766206736069</v>
+        <v>0.008110680169263718</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.009747469824794505</v>
+        <v>0.009283261384598956</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003415360967398818</v>
+        <v>0.0003404786498314793</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.0005267191605749075</v>
+        <v>0.0005242525596195048</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.000735359163302941</v>
+        <v>0.0007225842291893135</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009579613363027424</v>
+        <v>0.0009270892209148</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.001202682673070548</v>
+        <v>0.001145406738109851</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>529.0741670269539</v>
+        <v>527.4360741647978</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>828.2564196490328</v>
+        <v>824.3777339490579</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>1172.268664040896</v>
+        <v>1151.903574851923</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1546.819895127043</v>
+        <v>1496.970699259668</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1973.140430787675</v>
+        <v>1879.172615741679</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003448617287306076</v>
+        <v>0.003437939851674719</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005033106489159096</v>
+        <v>0.00500953668915172</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.006636116438922032</v>
+        <v>0.006520831344905104</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008075190706733527</v>
+        <v>0.007814952417534835</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.009378492822202452</v>
+        <v>0.008931856351135303</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0003961925906644028</v>
+        <v>0.0003949659190647414</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006101950860585869</v>
+        <v>0.0006073375712861771</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008506232625776512</v>
+        <v>0.000835845917468984</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.001106075326517426</v>
+        <v>0.001070429957738983</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.001385635093221035</v>
+        <v>0.001319646327226788</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>529.0741670269539</v>
+        <v>527.4360741647978</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>828.2564196490328</v>
+        <v>824.3777339490579</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>1172.268664040896</v>
+        <v>1151.903574851923</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1546.819895127043</v>
+        <v>1496.970699259668</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1973.140430787675</v>
+        <v>1879.172615741679</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>456.1535111072135</v>
+        <v>457.2542693458925</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>509.6415224562401</v>
+        <v>511.330401002335</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>558.4403689618165</v>
+        <v>565.1145504028025</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>600.5499545928174</v>
+        <v>612.5134779532567</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>642.435071877816</v>
+        <v>660.0090237161168</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>39.34378514124248</v>
+        <v>39.43872685402228</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>46.46312799181871</v>
+        <v>46.61710010082515</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>53.72199496514878</v>
+        <v>54.36405159589651</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>61.62109240855482</v>
+        <v>62.84864287773334</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>71.03030914749181</v>
+        <v>72.97335878263851</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>47075914.9240907</v>
+        <v>47189515.2799671</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>56455438.40305562</v>
+        <v>56642523.5884812</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>66170585.44240464</v>
+        <v>66961420.98697659</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>76852213.85339236</v>
+        <v>78383182.67406264</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>89974593.14276312</v>
+        <v>92435867.80813874</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>463.8509088875164</v>
+        <v>464.9702419564154</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>518.2415078299859</v>
+        <v>519.9588854880144</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>567.8638142533905</v>
+        <v>574.6506196864281</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>610.6839813510969</v>
+        <v>622.8493841137923</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>653.275892294298</v>
+        <v>671.1463971450768</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>47.91021385885063</v>
+        <v>48.02582748745998</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>56.51959465202611</v>
+        <v>56.70689244201335</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>65.27863904623896</v>
+        <v>66.05881452321103</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>74.77363489876616</v>
+        <v>76.26319645982379</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>86.04370739269072</v>
+        <v>88.39745181901554</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>47075914.9240907</v>
+        <v>47189515.2799671</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>56455438.40305562</v>
+        <v>56642523.5884812</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>66170585.44240464</v>
+        <v>66961420.98697659</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>76852213.85339236</v>
+        <v>78383182.67406264</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>89974593.14276312</v>
+        <v>92435867.80813874</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>906.4047888497507</v>
+        <v>910.5211570214989</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1030.020376359246</v>
+        <v>1036.66200069719</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1140.898619814335</v>
+        <v>1158.103772940741</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1218.83140545108</v>
+        <v>1246.884903886325</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1293.006067454048</v>
+        <v>1332.291034542985</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>59.26101965817956</v>
+        <v>59.5301490561562</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>68.45765238623447</v>
+        <v>68.89907084808475</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>78.45312861662099</v>
+        <v>79.63622943526713</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>89.13737808616851</v>
+        <v>91.18902795790503</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>101.9655727093285</v>
+        <v>105.063558301908</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>15717905.29718794</v>
+        <v>15789286.9645046</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>18260996.39591656</v>
+        <v>18378744.23943682</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>21034663.84028599</v>
+        <v>21351873.98152842</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>23998460.41759009</v>
+        <v>24550826.20728188</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>27625836.20539866</v>
+        <v>28465182.66590707</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>920.6559837956145</v>
+        <v>924.8370726815581</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1046.215150881935</v>
+        <v>1052.961199958541</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1158.836707569888</v>
+        <v>1176.312373379252</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1237.994812550095</v>
+        <v>1266.489389717527</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1313.335705779168</v>
+        <v>1353.238341410145</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>59.51258517114239</v>
+        <v>59.78285703469667</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>68.74915746681714</v>
+        <v>69.19245556841267</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>78.78938908278752</v>
+        <v>79.97756082772833</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>89.52416199621217</v>
+        <v>91.58471436403359</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>102.4151112868439</v>
+        <v>105.5267550583504</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>15717905.29718794</v>
+        <v>15789286.9645046</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>18260996.39591656</v>
+        <v>18378744.23943682</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>21034663.84028599</v>
+        <v>21351873.98152842</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>23998460.41759009</v>
+        <v>24550826.20728188</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>27625836.20539866</v>
+        <v>28465182.66590707</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>520.9253142767368</v>
+        <v>522.4598891477642</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>581.4346859436331</v>
+        <v>583.806861448624</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>636.8661517998537</v>
+        <v>644.9582884286416</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>682.9950257045423</v>
+        <v>697.1040754064026</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>728.5458577871523</v>
+        <v>748.9935199488988</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>42.95770712134171</v>
+        <v>43.08425466291568</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>50.42248980708948</v>
+        <v>50.6282068000943</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>58.14303450445336</v>
+        <v>58.88181042760876</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>66.50647352489707</v>
+        <v>67.88033878766421</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>76.48111878471741</v>
+        <v>78.6276687402855</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>62793820.22127864</v>
+        <v>62978802.2444717</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>74716434.79897219</v>
+        <v>75021267.82791802</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>87205249.28269063</v>
+        <v>88313294.96850501</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>100850674.2709824</v>
+        <v>102934008.8813445</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>117600429.3481618</v>
+        <v>120901050.4740458</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>529.629310136316</v>
+        <v>531.189525791075</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>591.1536662859879</v>
+        <v>593.5654939267371</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>647.5141328874428</v>
+        <v>655.7415646917366</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>694.4152751160225</v>
+        <v>708.7602399570713</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>740.7285814318559</v>
+        <v>761.5181688336326</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>50.36815660969364</v>
+        <v>50.5165343239549</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>59.08854170698634</v>
+        <v>59.32961502898029</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>68.09521366222606</v>
+        <v>68.96044377559281</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>77.82497663419359</v>
+        <v>79.43265520000053</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>89.40085212837451</v>
+        <v>91.91001253571751</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>62793820.22127864</v>
+        <v>62978802.2444717</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>74716434.79897219</v>
+        <v>75021267.82791802</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>87205249.28269063</v>
+        <v>88313294.96850501</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>100850674.2709824</v>
+        <v>102934008.8813445</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>117600429.3481618</v>
+        <v>120901050.4740458</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>916.8636062411915</v>
+        <v>920.7174815471433</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1025.743597368488</v>
+        <v>1031.788347073501</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1124.867408518502</v>
+        <v>1141.108897225733</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1216.101966930558</v>
+        <v>1243.344335676612</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1311.604254483835</v>
+        <v>1350.704363434102</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>91.83087404737363</v>
+        <v>92.2168690147887</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>106.4608024544716</v>
+        <v>107.0881803936398</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>121.300909132823</v>
+        <v>123.0523220824188</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>138.2560600880815</v>
+        <v>141.353187362534</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>158.0061940023745</v>
+        <v>162.7165015354505</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>5766105.047103525</v>
+        <v>5790341.858011155</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>6767384.744927467</v>
+        <v>6807265.224850081</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>7799159.069755712</v>
+        <v>7911767.856354091</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>8984825.692261012</v>
+        <v>9186098.234600028</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>10406230.31776842</v>
+        <v>10716449.45421551</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1164.368417620849</v>
+        <v>1169.262635976942</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1302.64026320015</v>
+        <v>1310.316776479801</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1428.522274822855</v>
+        <v>1449.148108782362</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1544.385351607079</v>
+        <v>1578.981722946462</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1665.668219288412</v>
+        <v>1715.323295220446</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>105.1315484100336</v>
+        <v>105.5734504285409</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>121.9289314107802</v>
+        <v>122.6474636775851</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>138.9868206206844</v>
+        <v>140.9935930282322</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>158.5157112353387</v>
+        <v>162.0666827615303</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>181.2947438412287</v>
+        <v>186.6993041055536</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>5766105.047103525</v>
+        <v>5790341.858011155</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>6767384.744927467</v>
+        <v>6807265.224850081</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>7799159.069755712</v>
+        <v>7911767.856354091</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>8984825.692261012</v>
+        <v>9186098.234600028</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>10406230.31776842</v>
+        <v>10716449.45421551</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>540.55788601468</v>
+        <v>542.2074632310088</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>603.1321085623804</v>
+        <v>605.6836308967225</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>660.3852683141049</v>
+        <v>668.8701612286803</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>708.3982444206448</v>
+        <v>723.1331133537849</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>755.8615597541253</v>
+        <v>777.1830703679593</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>44.97060968934483</v>
+        <v>45.10784289797466</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>52.72755069765644</v>
+        <v>52.95061214858948</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>60.73922601201266</v>
+        <v>61.51962777618557</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>69.45500450359408</v>
+        <v>70.89968677966056</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>79.82955212688481</v>
+        <v>82.08140184857811</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>68559925.26838216</v>
+        <v>68769144.10248286</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>81483819.54389966</v>
+        <v>81828533.05276811</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>95004408.35244635</v>
+        <v>96225062.8248591</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>109835499.9632435</v>
+        <v>112120107.1159445</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>128006659.6659302</v>
+        <v>131617499.9282613</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>555.078346375571</v>
+        <v>556.7722345180773</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>619.243771261224</v>
+        <v>621.8634532352801</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>677.9415301303848</v>
+        <v>686.6519928882605</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>727.1523837690162</v>
+        <v>742.2773437101854</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>775.7477883893105</v>
+        <v>797.6302541535191</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>52.67586632912666</v>
+        <v>52.8366130524564</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>61.73085229416029</v>
+        <v>61.99200179376489</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>71.07111372268386</v>
+        <v>71.98426369466318</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>81.20647303144564</v>
+        <v>82.8955889292688</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>93.24304117939315</v>
+        <v>95.87326157692111</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>68559925.26838216</v>
+        <v>68769144.10248286</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>81483819.54389966</v>
+        <v>81828533.05276811</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>95004408.35244635</v>
+        <v>96225062.8248591</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>109835499.9632435</v>
+        <v>112120107.1159445</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>128006659.6659302</v>
+        <v>131617499.9282613</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>3077.561852826309</v>
+        <v>3083.889998484762</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>3276.191295399594</v>
+        <v>3285.900259893121</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>3504.68561893784</v>
+        <v>3546.196578999231</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>3722.77992925921</v>
+        <v>3797.816070736524</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3974.814607493171</v>
+        <v>4087.332474382466</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>2731.81260038769</v>
+        <v>2737.429809358153</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>2904.711802170078</v>
+        <v>2913.319890406804</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>3108.026818208475</v>
+        <v>3144.839585785468</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>3299.321888233776</v>
+        <v>3365.822833411584</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3541.909197954798</v>
+        <v>3642.172507573858</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67209786.84825529</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78972532.32868001</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>94371570.14859995</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>112112151.776179</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>131462690.8423989</v>
+        <v>135184097.5015242</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>2243.029606695841</v>
+        <v>2247.641770072626</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>2387.797361743303</v>
+        <v>2394.87357851839</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>2554.331636980548</v>
+        <v>2584.586207602601</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>2713.28603611098</v>
+        <v>2767.974875833654</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>2896.977306092659</v>
+        <v>2978.984075991752</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>1981.266062581127</v>
+        <v>1985.339982401991</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>2106.56649620241</v>
+        <v>2112.809287746237</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>2254.035891186371</v>
+        <v>2280.733633588824</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>2392.709530264282</v>
+        <v>2440.936848085552</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>2569.179492848509</v>
+        <v>2641.90705997732</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67209786.84825529</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78972532.32868001</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>94371570.14859995</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>112112151.776179</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>131462690.8423989</v>
+        <v>135184097.5015242</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>912.5734325015558</v>
+        <v>914.90905523399</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>1006.837829461618</v>
+        <v>1010.470323126822</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>1104.397874821074</v>
+        <v>1118.038337945848</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>1190.524717508094</v>
+        <v>1214.90429732859</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1281.79911833712</v>
+        <v>1318.02099818898</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>87.5551248190278</v>
+        <v>87.77921170626917</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>101.891789530499</v>
+        <v>102.2593971721425</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>118.1017799659395</v>
+        <v>119.5604598595933</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>136.0826231340085</v>
+        <v>138.8693247657245</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>158.1536150088733</v>
+        <v>162.6228186142093</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>135631797.5603276</v>
+        <v>135978930.9507381</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>160223008.9675312</v>
+        <v>160801065.3814481</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>188271286.645392</v>
+        <v>190596632.9734591</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>219732572.5662038</v>
+        <v>224232258.8921236</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>259469350.5083291</v>
+        <v>266801597.4297855</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>884.0767342759235</v>
+        <v>886.3394231119669</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>973.6350326011251</v>
+        <v>977.1477364196097</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>1065.788260498024</v>
+        <v>1078.951854704048</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1147.116373110476</v>
+        <v>1170.60703632004</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1233.278383714673</v>
+        <v>1268.129134350827</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>101.566692537378</v>
+        <v>101.8266403591091</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>118.0398852651653</v>
+        <v>118.4657523938333</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>136.6136799596382</v>
+        <v>138.3010010839486</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>157.1228671892125</v>
+        <v>160.3404311976965</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>182.2119865721296</v>
+        <v>187.3610466633448</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>135631797.5603276</v>
+        <v>135978930.9507381</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>160223008.9675312</v>
+        <v>160801065.3814481</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>188271286.645392</v>
+        <v>190596632.9734591</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>219732572.5662038</v>
+        <v>224232258.8921236</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>259469350.5083291</v>
+        <v>266801597.4297855</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="C94" s="85" t="n">
-        <v>126831.7918250114</v>
+        <v>126831.7918250115</v>
       </c>
       <c r="D94" s="86" t="n">
         <v>135101.1136484238</v>
@@ -9768,7 +9768,7 @@
         <v>155047.6738590327</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>169351.9904723949</v>
+        <v>169351.990472395</v>
       </c>
       <c r="H94" s="85" t="n">
         <v>1397717.813839474</v>
@@ -9924,7 +9924,7 @@
         <v>32975.65810448211</v>
       </c>
       <c r="V95" s="80" t="n">
-        <v>36513.22206665209</v>
+        <v>36513.2220666521</v>
       </c>
       <c r="W95" s="80" t="n">
         <v>40503.3126402252</v>
@@ -9954,7 +9954,7 @@
         <v>37377.97480667131</v>
       </c>
       <c r="AF95" s="80" t="n">
-        <v>41377.72546463594</v>
+        <v>41377.72546463595</v>
       </c>
       <c r="AG95" s="80" t="n">
         <v>45929.96818582567</v>
@@ -10080,7 +10080,7 @@
         <v>1398476.087516877</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>1423997.15512468</v>
+        <v>1423997.155124681</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
